--- a/www/download/COUNTRY.BRA.EXI382.xlsx
+++ b/www/download/COUNTRY.BRA.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3281</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>84.621</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>72.216</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>70.414</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>71.761</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>72.347</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>74.08</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>75.019</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>77.655</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>78.752</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>79.961</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>84.365</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>86.982</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>89.098</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>90.573</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>91.528</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>92.483</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>92.921</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>93.359</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>94.637</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>91.576</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>90.025</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>75.659</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>76.626</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>85.471</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>76.646</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>78.776</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>76.472</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>56.982</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>42.363</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>42.802</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>42.814</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>43.065</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>43.456</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>45.732</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>48.182</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>48.908</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>49.728</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>53.127</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>54.684</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>56.818</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>58.749</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>60.13</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>61.511</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>62.524</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>63.538</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>64.922</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>62.52</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>61.764</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>51.48</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>51.846</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>59.099</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>52.794</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>54.102</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>51.703</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>186656.526</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>163323.3</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>159003.6</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>162086.1</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>163275.8</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>167222.8</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>168996.4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>174794.2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>177294.8</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>179369</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>188175.5</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>192590.1</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>196087.4</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>198229</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>200180.4</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>202133.3</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>203264.9</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>204397</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>207135.9</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>200665.358</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>197078.91</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>165989.879</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>167999.035</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>186701.928</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>167538.164</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>172283.954</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>168133.361</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>123207.397</t>
+          <t>161576906799.664</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23230.5</t>
+          <t>152832670084.625</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29395.2</t>
+          <t>148979762381.029</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26256.1</t>
+          <t>146260851002.967</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>26001.2</t>
+          <t>146569692080.48</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23683.6</t>
+          <t>152490873493.485</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>31055.8</t>
+          <t>153175998290.251</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>36698</t>
+          <t>156061589920.582</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>37400</t>
+          <t>157265224884.191</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>38017.8</t>
+          <t>164724238841.749</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>43146.5</t>
+          <t>177031065702.998</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>44338.7</t>
+          <t>179571405424.183</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>48761.2</t>
+          <t>179434256768.118</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>54090.4</t>
+          <t>188067086665.258</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>58013.6</t>
+          <t>179156280789.666</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>61935.5</t>
+          <t>183056886327.865</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>65611.3</t>
+          <t>183861713370.984</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>69289.8</t>
+          <t>181324232257.733</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>72614.5</t>
+          <t>187625670903.748</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>134871.933</t>
+          <t>174615767717.985</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>132962.689</t>
+          <t>164251815579.748</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>110980.208</t>
+          <t>143114730072.302</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>111640.732</t>
+          <t>148606656193.899</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>126566.487</t>
+          <t>158797925071.76</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>113048.47</t>
+          <t>141774569240.74</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>115864.326</t>
+          <t>145608489614.893</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>111452.054</t>
+          <t>148794088889.952</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>46486019116.6534</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>47447109198.3566</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>43668974143.5307</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>45968051452.0636</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>43077647240.335</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>43341436227.0178</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>44412420632.218</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>41724608749.8734</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>40160205832.4738</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>40654587732.7074</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>44493071452.7386</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>48085998018.3413</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>46027137119.4162</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>49924813917.708</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>49040847391.3027</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>51937851417.7071</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>51430829033.1814</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>50330605917.6151</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>52199912291.8751</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>46708037887.9216</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>42125762472.9701</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>37591298008.0277</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>40765804768.2968</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>42852926991.7336</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>37467385388.1775</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>39911215689.1054</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>42361758284.719</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>46455657.5084267</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>24092870.4562068</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>20081379.9889769</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>20165789.6345964</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>24946658.4005196</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>21390420.8000452</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>21145189.4766447</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>24459942.9786967</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>24886899.1657861</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>22837896.7854027</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>20624760.7079258</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>18417286.6604647</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>15254160.1641056</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>13942120.3587773</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>12756885.4489713</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>11203195.2762362</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>8584937.68074383</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>8082105.10902374</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>8359703.40067512</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>13894511.1393357</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>14801989.4085058</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>13050400.204693</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>14084102.9391831</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15027370.4830724</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>13544976.1918576</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12972182.1057405</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>12938269.4846626</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>389581.62130688</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>768307.663128487</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>804042.892351851</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>848621.429409456</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>891488.950139885</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1092099.96198214</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1093251.43847145</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1077977.80875492</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>993126.655959471</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>973109.276227593</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1103709.09270171</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1214904.1842844</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1236624.38836786</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1264599.75878396</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1257835.6699784</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1466249.47656724</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1499872.66119426</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1656411.8977099</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1649023.27759769</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1665117.7024768</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>1797992.08971825</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>1407093.32296418</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>1519899.5533729</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1587836.29012255</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1520539.81156365</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>1488157.31234893</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1488984.65421198</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>602294.504597723</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1161386.52958642</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1233049.47964544</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1244524.95484809</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1315506.20198263</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1636046.13751304</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1650126.96259507</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1629694.48787303</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1508610.94792337</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1544194.4936896</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1779121.80768239</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1930448.25773977</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1998522.98845968</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2104754.59244457</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2009264.40164235</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2367540.56302567</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2475571.24739702</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2694722.71870786</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2723757.97105778</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2623818.23060454</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2788034.48548267</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2214190.64034587</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2430772.54639866</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2526229.59683895</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2403060.62233423</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2347857.83243925</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2355508.65520871</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.65041833130665</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.510391667850247</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.326863051480877</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.428818512626584</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.396410861184682</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.45355756380624</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.300740658628581</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.120471081708748</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.0687298726513198</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.0648583070152317</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.0302647447940916</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.0779290889802219</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.0594011066421187</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.0834371879508906</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.182964876954886</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.192492533084735</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.275719276420331</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.376693142009484</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.391084712823925</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.88755295900381</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2.15632718038374</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.95228453364126</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.73858771339818</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.95350856568619</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2.01725005166235</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.90305178298881</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.63095911920604</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>815.802285677815</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1120.02089570213</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1020.25069140228</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1073.66117049829</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1000.3006462446</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>997.375159116943</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>971.143258940802</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>865.988164541702</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>821.131049726738</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>817.539167726578</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>837.477228417543</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>879.339882787894</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>810.084482817952</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>849.7912989512</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>815.577653014603</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>844.366884259652</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>822.576737002678</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>792.136427726982</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>804.045376144</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>747.092840854018</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>682.043840906186</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>730.20923531276</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>786.286299873456</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>725.107555482414</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>709.685629850571</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>737.697304316633</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>819.328869092901</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>-2972838405.48197</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>-4295662546.60955</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>-2361426717.03891</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>-1730700048.84459</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>-3708448872.83728</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>-2931540143.0752</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>-5555859597.64081</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>-3924852163.07137</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>-3417689723.78694</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>-2037519010.05367</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>-158320270.039784</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>1499648431.99888</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>560607785.116103</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>4357963687.87035</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>2783316707.15888</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>4468079943.63874</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.878</t>
+          <t>9078390941.73938</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.896</t>
+          <t>6744105978.82746</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>6038885707.34225</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>-2868747724.96959</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>-4598302091.26498</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-211551665.071635</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>1679704405.79137</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>-1609273759.9941</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>-983151721.271889</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-374947917.64679</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>588812671.141591</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2076319028.07665</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-2568228982.94339</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-764905342.129588</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-195940731.585297</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-2240391765.58017</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-1274740196.2068</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-3794437146.10769</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-2727188867.09607</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-2308692038.13964</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-899450704.394007</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1489730033.51595</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>3050003748.65125</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2228819573.59336</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>6694582622.7276</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>5872680386.32332</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>8270978076.07507</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>13000802306.8612</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>10853285186.7488</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>10609176823.0863</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1430850444.85987</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-369442495.507974</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>3804975302.95364</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>4466947125.71425</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>1305165088.48817</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1877085135.65371</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2849916357.13781</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>4526358669.24045</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-5049157433.55862</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-1727433563.66616</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-1596521374.90932</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-1534759317.2593</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-1468057107.25711</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-1656799946.86839</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1761422451.53312</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-1197663295.9753</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-1108997685.64731</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-1138068305.65966</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-1648050303.55574</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-1550355316.65237</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-1668211788.47726</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-2336618934.85725</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-3089363679.16443</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-3802898132.43633</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-3922411365.12182</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-4109179207.92137</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-4570291115.74401</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-4299598169.82946</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-4228859595.757</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-4016526968.02527</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-2787242719.92289</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-2914438848.48227</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-2860236856.9256</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-3224864274.7846</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-3937545998.09886</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>2162.21733268234</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>548.371562717593</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>686.768437135056</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.209</t>
+          <t>613.255384300294</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.918</t>
+          <t>603.770605623182</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>545.008111747001</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.067</t>
+          <t>679.080995624239</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>761.66163361239</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>764.694817248975</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>764.514961389191</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>812.131193828623</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>810.813726818258</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>858.204397570947</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>920.695495280823</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.155</t>
+          <t>964.799717945574</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2.899</t>
+          <t>1006.90120466366</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.278</t>
+          <t>1049.37699972925</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.345</t>
+          <t>1090.52878758763</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3.251</t>
+          <t>1118.49523117068</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.211</t>
+          <t>2157.27014325858</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2.775</t>
+          <t>2152.75351326552</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2.775</t>
+          <t>2155.78543173587</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2153.31400004677</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.745</t>
+          <t>2141.61137616108</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2.813</t>
+          <t>2141.29900333066</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2.868</t>
+          <t>2141.57347460244</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2.962</t>
+          <t>2155.62075976874</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>2205.79910291729</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>2261.58498842969</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>2258.10877021053</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>2258.70288333263</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>2256.85519430078</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>2257.3424496654</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>2252.70563708278</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>2250.91591365263</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>2251.30250494872</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>2243.21167371949</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>2230.50043442426</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>2214.14758983571</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>2200.80585422721</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>2188.60304306044</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>2187.09943864084</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>2185.62654758137</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.878</t>
+          <t>2187.50346396529</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.896</t>
+          <t>2189.36109135542</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>2188.74581558101</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>2191.2425273866</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>2189.15667852691</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>2193.90725185675</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>2192.46505441908</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>2184.38083979695</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>2185.86242076113</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>2187.02309651633</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>2198.63629304398</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>43791.8778708171</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>46454.3582364772</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>51297.831818303</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>51370.3397641255</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>53485.2404813321</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>74783.5840954365</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>87619.3709542372</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>92830.593704902</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>90189.0810166117</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>106092.860937988</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>130330.517566769</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>153060.124577313</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>165596.685104723</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>187219.555323518</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>157562.177740868</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>216712.948922433</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>260620.445480326</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>273077.045281307</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>261893.956829445</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>245771.946099333</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>258331.907235405</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>251123.52432569</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>286095.7401968</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>296049.48900691</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>294328.160256423</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>314646.034889359</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>328519.157483971</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10120098624.6512</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7528364437.43946</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>7340895668.3268</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>7128190193.62593</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>9537399533.49346</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>9812200365.68551</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>13301146908.9172</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>15718717552.7827</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>16123466748.5284</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>18135055442.456</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>17828931430.1569</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>17421966059.3073</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>16573440987.1749</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>16341906311.5385</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>14709732943.6766</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>14756130330.9761</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>14711668166.4732</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>15423671659.5313</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>15357488325.981</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>17013189849.276</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>18648764146.7804</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>16632263845.3369</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>18263541544.7133</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>21539289870.588</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>18566353114.5304</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>20163350807.0397</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>19370973918.5337</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>59813.8582581425</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>66755.1908112864</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>79390.8392379915</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>76840.7399601256</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>68601.8344425937</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>97779.6503946403</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>105191.884018595</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>87367.8547192817</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>75865.5620065205</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>82070.9870854392</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>98449.7942265308</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>121826.141821877</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>147425.916298994</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>190078.520756841</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>163865.752205981</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>239400.108278366</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>279533.990764645</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>307189.359710721</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>317944.437832837</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>310131.377636698</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>282834.225748241</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>242642.670324303</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>268936.486072774</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>288080.244029527</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>301491.332259058</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>321909.742467982</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>340768.156312622</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>186656.526</t>
+          <t>16224132520.5221</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>163323.3</t>
+          <t>7356573409.43536</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>159003.6</t>
+          <t>10238134879.0863</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>162086.1</t>
+          <t>10196070764.8457</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>163275.8</t>
+          <t>8601997503.63762</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>167222.8</t>
+          <t>10448283248.7561</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>168996.4</t>
+          <t>10579364444.7208</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>174794.2</t>
+          <t>10879765878.4377</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>177294.8</t>
+          <t>10272531173.973</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>179369</t>
+          <t>11692168790.4548</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>188175.5</t>
+          <t>12338541553.0226</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>192590.1</t>
+          <t>14274257112.0321</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>196087.4</t>
+          <t>14877559019.1394</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>198229</t>
+          <t>21091660762.4835</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>200180.4</t>
+          <t>18420881664.2968</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>202133.3</t>
+          <t>22021582769.2436</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>203264.9</t>
+          <t>25971088868.2067</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>204397</t>
+          <t>25887085291.4465</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>207135.9</t>
+          <t>27817155993.065</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>200665.358</t>
+          <t>20986241809.2394</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>197078.91</t>
+          <t>16418975817.6427</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>165989.879</t>
+          <t>15521262218.6761</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>167999.035</t>
+          <t>18290419284.8192</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>186701.928</t>
+          <t>19137955194.0154</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>167538.164</t>
+          <t>18236965521.3698</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>172283.954</t>
+          <t>20493282707.6015</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>168133.361</t>
+          <t>21153268696.7983</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>123207.397</t>
+          <t>-16021.9803873255</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>23230.5</t>
+          <t>-20300.8325748091</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>29395.2</t>
+          <t>-28093.0074196885</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>26256.1</t>
+          <t>-25470.4001960002</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>26001.2</t>
+          <t>-15116.5939612616</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23683.6</t>
+          <t>-22996.0662992038</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>31055.8</t>
+          <t>-17572.513064358</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>36698</t>
+          <t>5462.7389856203</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>37400</t>
+          <t>14323.5190100913</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>38017.8</t>
+          <t>24021.8738525488</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>43146.5</t>
+          <t>31880.7233402383</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>44338.7</t>
+          <t>31233.9827554359</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>48761.2</t>
+          <t>18170.7688057291</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>54090.4</t>
+          <t>-2858.96543332373</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>58013.6</t>
+          <t>-6303.57446511226</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>61935.5</t>
+          <t>-22687.1593559332</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>65611.3</t>
+          <t>-18913.5452843195</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>69289.8</t>
+          <t>-34112.3144294142</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>72614.5</t>
+          <t>-56050.4810033923</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>134871.933</t>
+          <t>-64359.4315373647</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>132962.689</t>
+          <t>-24502.3185128352</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>110980.208</t>
+          <t>8480.85400138761</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>111640.732</t>
+          <t>17159.2541240257</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>126566.487</t>
+          <t>7969.24497738259</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>113048.47</t>
+          <t>-7163.17200263525</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>115864.326</t>
+          <t>-7263.70757862263</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>111452.054</t>
+          <t>-12248.9988286504</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>162861.358</t>
+          <t>-6104033895.87091</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>155374.663</t>
+          <t>171791028.004094</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>150825.482</t>
+          <t>-2897239210.75953</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>148234.743</t>
+          <t>-3067880571.2198</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>148549.06</t>
+          <t>935402029.855831</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>154255.297</t>
+          <t>-636082883.070542</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>154913.247</t>
+          <t>2721782464.19645</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>157838.884</t>
+          <t>4838951674.34506</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>159027.348</t>
+          <t>5850935574.55545</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>166551.036</t>
+          <t>6442886652.00122</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>178954.056</t>
+          <t>5490389877.13426</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>181316.183</t>
+          <t>3147708947.27519</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>181137.353</t>
+          <t>1695881968.03554</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>189024.392</t>
+          <t>-4749754450.94494</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>180467.003</t>
+          <t>-3711148720.62015</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>183649.957</t>
+          <t>-7265452438.26747</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>183813.184</t>
+          <t>-11259420701.7335</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>181364.336</t>
+          <t>-10463413631.9151</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>187253.257</t>
+          <t>-12459667667.084</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>175594.804</t>
+          <t>-3973051959.96342</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>165898.52</t>
+          <t>2229788329.13776</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>143824.301</t>
+          <t>1111001626.66072</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>149502.964</t>
+          <t>-26877740.1058472</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>159949.338</t>
+          <t>2401334676.57257</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>142730.231</t>
+          <t>329387593.160603</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>146223.745</t>
+          <t>-329931900.561795</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>149373.283</t>
+          <t>-1782294778.26462</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>246954.231877669</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>270213.703830078</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>313020.526148423</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>314264.068561784</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.156</t>
+          <t>224599.257082153</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.436</t>
+          <t>284208.157621484</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>255317.417064125</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.434</t>
+          <t>220599.355785523</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>201578.624108619</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>219923.437259411</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>295734.785548698</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>337244.602598712</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>413190.25743803</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.859</t>
+          <t>474276.710739464</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.767</t>
+          <t>504434.988649804</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>708365.004573121</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2.159</t>
+          <t>816328.706577004</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.351</t>
+          <t>817180.473201118</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>781290.997928657</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2.273</t>
+          <t>761837.488022785</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>2.398</t>
+          <t>668061.759433691</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>1.887</t>
+          <t>662562.960162556</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2.058</t>
+          <t>722294.767704033</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>654148.355304874</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>666616.129866169</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>1.971</t>
+          <t>676880.809096433</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1.976</t>
+          <t>702983.365549312</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>104512.648</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>101105.453</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>97146.239</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>99732.908</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>99326.982</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>101791.309</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>101483.028</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>103228.508</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>103528.539</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>103804.725</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>109824.294</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>113011.085</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>111028.384</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>112996.353</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>112155.055</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>113369.573</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>111396.171</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>111457.707</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>113592.728</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>110814.005</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>105925.327</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>90947.806</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>92919.92</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>99810.844</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>89708.048</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>92291.933</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>94057.016</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>368096.300987938</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>427391.041370651</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>473674.038022653</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>472411.739936025</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>347852.356428172</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>416738.292762905</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>375595.677628965</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>317300.308441144</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>281571.85707335</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>302853.28139726</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>406452.845203183</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.062</t>
+          <t>501052.627508162</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>596347.326719196</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>684155.294353757</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.098</t>
+          <t>741809.701320059</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>1029851.42274988</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1166209.65203946</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1189332.52998873</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1154604.39063755</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1150641.91302489</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1018669.92381262</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1023119.80230013</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>1.279</t>
+          <t>1132797.41304694</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1017753.79047634</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>1032373.48460109</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1048606.23989371</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1100168.52504271</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>45516.028</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>47226.566</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>43258.006</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>45406.115</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>42584.906</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>42741.506</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>43918.835</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>41166.825</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>39785.736</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>40129.511</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>44152.115</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>47514.94</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>45523.953</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>49105.215</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>48194.888</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>50931.028</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>50172.364</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>48990.243</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>50860.591</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>45834.49</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>41423.37</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>36834.488</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>39886.052</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>41877.759</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>36669.06</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>38923.361</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>41153.246</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>170.69</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-50.81</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-32.05</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-42.17</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-38.94</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-44.59</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-29.29</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-10.86</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-5.26</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-6.68</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>7.11</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>10.15</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>21.61</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>30.77</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>41.44</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>42.77</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>194.26</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>220.98</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>201.29</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>179.9</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>202.23</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>208.29</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>197.67</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>170.82</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>61.078</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>32.066</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>26.582</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>26.708</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>33.051</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>28.272</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>27.908</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>32.321</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>32.836</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>30.118</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>27.205</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>24.286</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>20.111</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>18.306</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>16.768</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>14.704</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>11.186</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>10.53</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>10.886</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>18.289</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>19.542</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>17.17</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>18.577</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>19.843</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>17.855</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>17.083</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>17.035</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>368443.715306596</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>405376.497813379</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>496427.824540776</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>474637.185527654</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>343599.851402662</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>451111.223225969</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>392090.444406191</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>343713.953808965</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>319163.239728448</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>349886.990140211</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>467060.643126605</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>572921.153530848</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>642489.479407551</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>712434.193715716</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>715908.420265966</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>994855.310688666</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1119176.71195283</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1143983.40170973</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1110767.79805243</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1102275.34955594</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>957590.659511933</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>950320.677079087</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>1078864.88186677</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>925688.497447568</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>977465.373817993</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>1001664.43912813</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1000756.28945059</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>123207397216.25</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>23230499999.9346</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>29395199999.9367</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>26256100000.0474</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>26001199999.9839</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>23683600000.0281</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>31055799999.9952</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>36697999999.9019</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>37399999999.9571</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>38017799999.9618</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>43146500000.1162</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>44338700000.0672</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>48761199999.8781</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>54090399999.9731</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>58013600000.0157</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>61935500000.0801</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>65611299999.9079</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>69289799999.9627</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>72614499999.9771</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>134871933012.53</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>132962689087.825</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>110980207708.6</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>111640732065.247</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>126566486934.81</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>113048470498.132</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>115864325867.508</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>111452054264.783</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>186656525506.772</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>163323299999.937</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>159003599999.965</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>162086099999.972</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>163275799999.992</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>167222800000.007</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>168996400000.032</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>174794199999.964</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>177294799999.999</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>179368999999.939</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>188175500000.021</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>192590100000.036</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>196087399999.975</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>198228999999.983</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>200180400000.042</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>202133299999.998</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>203264899999.891</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>204397000000.022</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>207135899999.98</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>200665358062.658</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>197078909720.836</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>165989879342.868</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>167999035398.614</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>186701927513.837</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>167538163734.947</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>172283954069.918</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>168133360743.209</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>104512647610.502</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>101105453362.043</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>97146238674.2003</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>99732907694.0296</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>99326982053.1635</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>101791308525.081</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>101483027831.241</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>103228508156.128</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>103528538688.481</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>103804725046.932</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>109824294246.386</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>113011084836.38</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>111028384116.379</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>112996352774.723</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>112155055498.774</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>113369573451.888</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>111396170728.448</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>111457707158.398</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>113592728165.568</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>110814004784.09</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>105925327205.241</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>90947806134.2995</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>92919919929.153</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>99810844010.6193</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>89708047643.1901</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>92291933338.81</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>94057015882.6105</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>84620818.4870092</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>72216300.0000008</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>70414499.9999894</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>71760700.0000021</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>72346599.9999958</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>74079500.0000084</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>75019300.0000121</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77654700.000019</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>78752100.000012</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>79960799.9999954</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>84364699.9999769</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>86981599.9999919</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>89098000.0000177</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>90573299.9999803</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>91527800.000005</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>92483000.0000136</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>92920949.999975</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>93359199.9999787</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>94636800.0000015</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>91576060.4107947</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>90025036.4233644</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>75659478.8600962</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>76625638.8260328</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>85471326.2963758</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>76646252.8216248</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>78775553.0997118</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>76471657.1245312</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>56981967.2398076</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>42362699.9999964</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>42802199.9999922</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>42814299.9999988</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>43064700.0000053</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>43455500.0000115</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>45732100.0000117</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>48181500.0000085</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>48908400.0000226</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>49728000.0000001</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>53127499.9999828</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>54684199.9999904</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>56817700.0000132</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>58749499.99997</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>60130200.0000049</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>61511000.0000139</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>62524049.9999867</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>63537799.9999794</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>64921600.0000059</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>62519723.5654522</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>61764009.7988428</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>51480173.3395316</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>51846006.6961075</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>59098718.0697952</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>52794341.342471</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>54102428.5375113</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>51702997.2733888</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>186656525506.772</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>163323299999.937</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>159003599999.965</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>162086099999.972</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>163275799999.992</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>167222800000.007</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>168996400000.032</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>174794199999.964</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>177294799999.999</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>179368999999.939</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>188175500000.021</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>192590100000.036</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>196087399999.975</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>198228999999.983</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>200180400000.042</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>202133299999.998</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>203264899999.891</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>204397000000.022</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>207135899999.98</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>200665358062.658</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>197078909720.836</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>165989879342.868</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>167999035398.614</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>186701927513.837</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>167538163734.947</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>172283954069.918</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>168133360743.209</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>123207397216.25</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>23230499999.9346</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>29395199999.9367</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>26256100000.0474</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>26001199999.9839</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>23683600000.0281</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>31055799999.9952</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>36697999999.9019</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>37399999999.9571</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>38017799999.9618</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>43146500000.1162</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>44338700000.0672</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>48761199999.8781</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>54090399999.9731</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>58013600000.0157</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>61935500000.0801</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>65611299999.9079</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>69289799999.9627</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>72614499999.9771</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>134871933012.53</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>132962689087.825</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>110980207708.6</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>111640732065.247</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>126566486934.81</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>113048470498.132</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>115864325867.508</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>111452054264.783</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1267036.31051026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1428630.05252789</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1652047.54641086</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1605159.64864835</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1219767.76969576</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1600676.03387012</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1417228.1274433</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1247485.55294219</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1157450.1409717</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1337502.15615362</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1806744.85066281</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2146728.8787464</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2482016.15057104</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2815588.01518293</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2861931.50348528</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>3849725.66905751</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>4353627.77785888</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>4442133.90022994</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>4317646.36843504</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>4264885.00324592</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>3685940.41741125</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>3685808.61950663</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>4130991.88975061</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>3645307.67576411</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>3735418.88773061</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>3809190.6250401</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>3934149.52359463</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>421565.422642747</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>483324.293932423</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>535967.730572956</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>536826.710079462</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>396676.192655714</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>486956.597160369</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>439450.187460806</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>375434.966158984</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>337046.540318879</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>364706.746068484</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>484775.129798719</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>598661.385049562</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>711401.386589173</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>818885.867410992</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>871371.317694379</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1217981.59964033</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1376884.77468782</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1404327.38368828</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1362051.56420674</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1353028.92271325</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>1199703.39782009</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>1204219.23288698</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>1346252.38105513</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>1194626.44085582</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>1214636.15785366</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>1235134.042775</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1289076.68445808</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
